--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059DA705-A33C-4B2C-B8BB-423A0A9688D4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4F4035-FC8D-41F9-855C-F5934839086B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15096" windowHeight="6060" activeTab="4" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4F4035-FC8D-41F9-855C-F5934839086B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D661896-1E84-4764-A132-AE74A99323B6}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15096" windowHeight="6060" activeTab="4" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="5" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -67,13 +67,13 @@
     <t>Automation Test Description</t>
   </si>
   <si>
-    <t>Automation Strategic Plan Regression</t>
-  </si>
-  <si>
-    <t>Automation Strategic Goal Regression</t>
-  </si>
-  <si>
-    <t>Automation Objective Regression</t>
+    <t xml:space="preserve">Automation Objective </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Strategic Plan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Strategic Goal </t>
   </si>
 </sst>
 </file>
@@ -457,7 +457,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -553,7 +553,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D661896-1E84-4764-A132-AE74A99323B6}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCABEC70-3983-4C99-A482-F7E121EF2354}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="5" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -67,13 +67,13 @@
     <t>Automation Test Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Objective </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Strategic Plan </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Strategic Goal </t>
+    <t>Permanent Objective Automation</t>
+  </si>
+  <si>
+    <t>Permanent Strategic Goal Automation</t>
+  </si>
+  <si>
+    <t>Permanent Strategic Plan for Automation</t>
   </si>
 </sst>
 </file>
@@ -432,13 +432,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -457,10 +457,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -471,7 +471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -490,14 +490,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -527,14 +527,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -545,7 +545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -553,7 +553,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +564,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,7 +581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -600,13 +600,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.21875" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,7 +617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -630,19 +630,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -653,7 +654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCABEC70-3983-4C99-A482-F7E121EF2354}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42E66E8-F5B9-480C-94F1-E0F730B683E2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -67,13 +67,13 @@
     <t>Automation Test Description</t>
   </si>
   <si>
-    <t>Permanent Objective Automation</t>
-  </si>
-  <si>
-    <t>Permanent Strategic Goal Automation</t>
-  </si>
-  <si>
-    <t>Permanent Strategic Plan for Automation</t>
+    <t>Automation Execution Strategic Goal</t>
+  </si>
+  <si>
+    <t>Automation Execution Strategic Plan</t>
+  </si>
+  <si>
+    <t>Automation Execution Objective</t>
   </si>
 </sst>
 </file>
@@ -457,7 +457,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +625,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42E66E8-F5B9-480C-94F1-E0F730B683E2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90B1328-D10E-4835-BB77-5600A82CD7F4}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -70,10 +70,10 @@
     <t>Automation Execution Strategic Goal</t>
   </si>
   <si>
+    <t>Automation Execution Objective</t>
+  </si>
+  <si>
     <t>Automation Execution Strategic Plan</t>
-  </si>
-  <si>
-    <t>Automation Execution Objective</t>
   </si>
 </sst>
 </file>
@@ -432,13 +432,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -457,10 +457,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -471,7 +471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -490,14 +490,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -527,14 +527,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -545,7 +545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -564,13 +564,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,7 +581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -600,13 +600,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,7 +617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -625,7 +625,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -637,13 +637,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90B1328-D10E-4835-BB77-5600A82CD7F4}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28502100-4512-4362-8D47-166A85812669}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="15">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -74,19 +74,31 @@
   </si>
   <si>
     <t>Automation Execution Strategic Plan</t>
+  </si>
+  <si>
+    <t>fieldStrategyDescription__c</t>
+  </si>
+  <si>
+    <t>fieldStrategyTitle__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -117,6 +129,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,13 +445,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -460,7 +473,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -471,7 +484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -490,14 +503,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,124 +521,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -634,16 +538,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28502100-4512-4362-8D47-166A85812669}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98980FE7-032B-4FE8-8842-C85F691DE542}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -445,13 +445,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,7 +462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -473,7 +473,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -484,7 +484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -503,14 +503,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -541,14 +541,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,7 +559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -579,13 +579,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -615,13 +615,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -652,13 +652,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98980FE7-032B-4FE8-8842-C85F691DE542}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B20792-6D33-44CB-81EA-51D257FC3A01}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" firstSheet="1" activeTab="5" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -73,13 +73,13 @@
     <t>Automation Execution Objective</t>
   </si>
   <si>
-    <t>Automation Execution Strategic Plan</t>
-  </si>
-  <si>
     <t>fieldStrategyDescription__c</t>
   </si>
   <si>
     <t>fieldStrategyTitle__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Execution Strategic Plan</t>
   </si>
 </sst>
 </file>
@@ -445,13 +445,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.69140625" customWidth="1"/>
+    <col min="3" max="3" width="38.765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,7 +462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -470,10 +470,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -484,7 +484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -503,14 +503,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.07421875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.4609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,12 +521,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -541,14 +541,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69140625" customWidth="1"/>
+    <col min="2" max="2" width="17.53515625" customWidth="1"/>
+    <col min="3" max="3" width="34.07421875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,12 +559,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -579,13 +579,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.07421875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.07421875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -615,13 +615,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -652,13 +652,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.07421875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.07421875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B20792-6D33-44CB-81EA-51D257FC3A01}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1564C219-B6E0-42B8-B105-5F89965692A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" firstSheet="1" activeTab="5" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="1" activeTab="1" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -445,13 +445,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="16.69140625" customWidth="1"/>
-    <col min="3" max="3" width="38.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="38.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,7 +462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -473,7 +473,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -484,7 +484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -503,14 +503,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.4609375" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -541,14 +541,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.69140625" customWidth="1"/>
-    <col min="2" max="2" width="17.53515625" customWidth="1"/>
-    <col min="3" max="3" width="34.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.53125" customWidth="1"/>
+    <col min="3" max="3" width="34.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,7 +559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -579,13 +579,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="21.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -615,13 +615,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="14.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.3046875" customWidth="1"/>
+    <col min="2" max="2" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -652,13 +652,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="21.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1564C219-B6E0-42B8-B105-5F89965692A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EA89C5-7BB0-46CA-9F44-B5E831F828CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="1" activeTab="1" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -52,12 +52,6 @@
     <t>StrategyTitle__c</t>
   </si>
   <si>
-    <t>StartDate__c</t>
-  </si>
-  <si>
-    <t>EndDate__c</t>
-  </si>
-  <si>
     <t>Overview</t>
   </si>
   <si>
@@ -80,13 +74,19 @@
   </si>
   <si>
     <t>Automation Runtime Execution Strategic Plan</t>
+  </si>
+  <si>
+    <t>fieldStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldEndDate__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +97,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -121,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -130,6 +136,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,13 +452,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="38.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,34 +469,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C4">
         <v>730</v>
@@ -503,14 +510,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.46484375" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,15 +528,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -541,14 +548,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.53125" customWidth="1"/>
-    <col min="3" max="3" width="34.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,15 +566,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -579,13 +586,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,15 +603,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -615,13 +622,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -640,7 +647,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -652,13 +659,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,15 +676,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
